--- a/FILTER.xlsx
+++ b/FILTER.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SOFTWARE\GIT HUB\pdf-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0422D24D-CF82-4D3B-B9A9-71C63B467BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F656DCE8-EEBF-42E6-B319-2F05A28308B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="275">
   <si>
     <t>AIMEX III;AIMEX IIIc;NXT III;NXT IIIc;NXT-H</t>
   </si>
@@ -844,6 +844,12 @@
   </si>
   <si>
     <t>AIMEX III;AIMEX IIS</t>
+  </si>
+  <si>
+    <t>nexim</t>
+  </si>
+  <si>
+    <t>GPX CL</t>
   </si>
 </sst>
 </file>
@@ -1177,6 +1183,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:N144"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -2285,6 +2292,9 @@
       <c r="F28" t="s">
         <v>142</v>
       </c>
+      <c r="G28" t="s">
+        <v>149</v>
+      </c>
       <c r="H28" t="s">
         <v>240</v>
       </c>
@@ -2366,6 +2376,9 @@
       <c r="A31" t="s">
         <v>246</v>
       </c>
+      <c r="D31" t="s">
+        <v>274</v>
+      </c>
       <c r="F31" t="s">
         <v>247</v>
       </c>
@@ -2696,6 +2709,9 @@
       </c>
       <c r="L45" t="s">
         <v>48</v>
+      </c>
+      <c r="M45" t="s">
+        <v>273</v>
       </c>
       <c r="N45" t="s">
         <v>43</v>

--- a/FILTER.xlsx
+++ b/FILTER.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SOFTWARE\GIT HUB\pdf-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F656DCE8-EEBF-42E6-B319-2F05A28308B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25391442-90B7-4B55-ABA7-0DF671C010A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="276">
   <si>
     <t>AIMEX III;AIMEX IIIc;NXT III;NXT IIIc;NXT-H</t>
   </si>
@@ -850,6 +850,9 @@
   </si>
   <si>
     <t>GPX CL</t>
+  </si>
+  <si>
+    <t>GPX_CII;GPX_CSII;</t>
   </si>
 </sst>
 </file>
@@ -2094,8 +2097,14 @@
       <c r="A22" t="s">
         <v>224</v>
       </c>
+      <c r="B22" t="s">
+        <v>275</v>
+      </c>
       <c r="D22" t="s">
         <v>102</v>
+      </c>
+      <c r="E22" t="s">
+        <v>275</v>
       </c>
       <c r="F22" t="s">
         <v>217</v>

--- a/FILTER.xlsx
+++ b/FILTER.xlsx
@@ -8,24 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SOFTWARE\GIT HUB\pdf-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25391442-90B7-4B55-ABA7-0DF671C010A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6EBF469-378A-41F6-A810-6AE2F3AB8B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="277">
   <si>
     <t>AIMEX III;AIMEX IIIc;NXT III;NXT IIIc;NXT-H</t>
   </si>
@@ -853,6 +864,9 @@
   </si>
   <si>
     <t>GPX_CII;GPX_CSII;</t>
+  </si>
+  <si>
+    <t>GPX_CL;</t>
   </si>
 </sst>
 </file>
@@ -2414,6 +2428,9 @@
       <c r="A32" t="s">
         <v>215</v>
       </c>
+      <c r="D32" t="s">
+        <v>276</v>
+      </c>
       <c r="F32" t="s">
         <v>238</v>
       </c>

--- a/FILTER.xlsx
+++ b/FILTER.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SOFTWARE\GIT HUB\pdf-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6EBF469-378A-41F6-A810-6AE2F3AB8B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DA5CAC0-BB43-44BB-911B-E8B1B55F92BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="278">
   <si>
     <t>AIMEX III;AIMEX IIIc;NXT III;NXT IIIc;NXT-H</t>
   </si>
@@ -857,9 +857,6 @@
     <t>AIMEX III;AIMEX IIS</t>
   </si>
   <si>
-    <t>nexim</t>
-  </si>
-  <si>
     <t>GPX CL</t>
   </si>
   <si>
@@ -867,6 +864,12 @@
   </si>
   <si>
     <t>GPX_CL;</t>
+  </si>
+  <si>
+    <t>NEXIM</t>
+  </si>
+  <si>
+    <t>NXTR_S;NXTR_A;AIMEXR;NXT_III;NXT_IIIc;NXT_II;NXT_IIc;NXT;AIMEX_III;AIMEX_IIIc;AIMEX_II;AIMEX_IIS;AIMEX;</t>
   </si>
 </sst>
 </file>
@@ -1201,7 +1204,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:N144"/>
+  <dimension ref="A1:N145"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -2112,13 +2115,13 @@
         <v>224</v>
       </c>
       <c r="B22" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D22" t="s">
         <v>102</v>
       </c>
       <c r="E22" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F22" t="s">
         <v>217</v>
@@ -2315,9 +2318,6 @@
       <c r="F28" t="s">
         <v>142</v>
       </c>
-      <c r="G28" t="s">
-        <v>149</v>
-      </c>
       <c r="H28" t="s">
         <v>240</v>
       </c>
@@ -2400,7 +2400,7 @@
         <v>246</v>
       </c>
       <c r="D31" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F31" t="s">
         <v>247</v>
@@ -2429,7 +2429,7 @@
         <v>215</v>
       </c>
       <c r="D32" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F32" t="s">
         <v>238</v>
@@ -2737,7 +2737,7 @@
         <v>48</v>
       </c>
       <c r="M45" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="N45" t="s">
         <v>43</v>
@@ -3027,6 +3027,9 @@
       </c>
     </row>
     <row r="66" spans="9:14" x14ac:dyDescent="0.3">
+      <c r="I66" t="s">
+        <v>277</v>
+      </c>
       <c r="J66" t="s">
         <v>200</v>
       </c>
@@ -3470,6 +3473,9 @@
       </c>
     </row>
     <row r="121" spans="12:14" x14ac:dyDescent="0.3">
+      <c r="L121" t="s">
+        <v>277</v>
+      </c>
       <c r="N121" t="s">
         <v>119</v>
       </c>
@@ -3587,6 +3593,11 @@
     <row r="144" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N144" t="s">
         <v>142</v>
+      </c>
+    </row>
+    <row r="145" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N145" t="s">
+        <v>277</v>
       </c>
     </row>
   </sheetData>

--- a/FILTER.xlsx
+++ b/FILTER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SOFTWARE\GIT HUB\pdf-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DA5CAC0-BB43-44BB-911B-E8B1B55F92BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F3FC37B-207C-4707-9981-FEB5C75BE901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="278">
   <si>
     <t>AIMEX III;AIMEX IIIc;NXT III;NXT IIIc;NXT-H</t>
   </si>
@@ -2318,6 +2318,9 @@
       <c r="F28" t="s">
         <v>142</v>
       </c>
+      <c r="G28" t="s">
+        <v>162</v>
+      </c>
       <c r="H28" t="s">
         <v>240</v>
       </c>
@@ -2346,6 +2349,9 @@
       </c>
       <c r="F29" t="s">
         <v>230</v>
+      </c>
+      <c r="G29" t="s">
+        <v>149</v>
       </c>
       <c r="H29" t="s">
         <v>134</v>

--- a/FILTER.xlsx
+++ b/FILTER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SOFTWARE\GIT HUB\pdf-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F3FC37B-207C-4707-9981-FEB5C75BE901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD4FD3E1-A153-4259-A787-12E3E7D0CA29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="281">
   <si>
     <t>AIMEX III;AIMEX IIIc;NXT III;NXT IIIc;NXT-H</t>
   </si>
@@ -870,6 +870,15 @@
   </si>
   <si>
     <t>NXTR_S;NXTR_A;AIMEXR;NXT_III;NXT_IIIc;NXT_II;NXT_IIc;NXT;AIMEX_III;AIMEX_IIIc;AIMEX_II;AIMEX_IIS;AIMEX;</t>
+  </si>
+  <si>
+    <t>NXTR_S;NXTR_A;</t>
+  </si>
+  <si>
+    <t>GPX_CII;GPX_CSII;GPX_CL;</t>
+  </si>
+  <si>
+    <t>fujitrax</t>
   </si>
 </sst>
 </file>
@@ -2152,8 +2161,14 @@
       <c r="A23" t="s">
         <v>226</v>
       </c>
+      <c r="B23" t="s">
+        <v>279</v>
+      </c>
       <c r="D23" t="s">
         <v>104</v>
+      </c>
+      <c r="E23" t="s">
+        <v>279</v>
       </c>
       <c r="F23" t="s">
         <v>221</v>
@@ -2319,7 +2334,7 @@
         <v>142</v>
       </c>
       <c r="G28" t="s">
-        <v>162</v>
+        <v>280</v>
       </c>
       <c r="H28" t="s">
         <v>240</v>
@@ -2351,7 +2366,7 @@
         <v>230</v>
       </c>
       <c r="G29" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="H29" t="s">
         <v>134</v>
@@ -2463,6 +2478,9 @@
       <c r="A33" t="s">
         <v>248</v>
       </c>
+      <c r="D33" t="s">
+        <v>279</v>
+      </c>
       <c r="H33" t="s">
         <v>212</v>
       </c>
@@ -3047,6 +3065,12 @@
       </c>
     </row>
     <row r="67" spans="9:14" x14ac:dyDescent="0.3">
+      <c r="I67" t="s">
+        <v>278</v>
+      </c>
+      <c r="J67" t="s">
+        <v>279</v>
+      </c>
       <c r="L67" t="s">
         <v>73</v>
       </c>

--- a/FILTER.xlsx
+++ b/FILTER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SOFTWARE\GIT HUB\pdf-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD4FD3E1-A153-4259-A787-12E3E7D0CA29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B65BA9A-F326-4778-A281-78A59CA6B78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="282">
   <si>
     <t>AIMEX III;AIMEX IIIc;NXT III;NXT IIIc;NXT-H</t>
   </si>
@@ -879,6 +879,9 @@
   </si>
   <si>
     <t>fujitrax</t>
+  </si>
+  <si>
+    <t>KNOWLEDGE</t>
   </si>
 </sst>
 </file>
@@ -902,7 +905,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -925,13 +928,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1213,10 +1228,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:N145"/>
+  <dimension ref="A1:O145"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>143</v>
       </c>
@@ -1259,8 +1274,11 @@
       <c r="N1" s="1" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O1" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>157</v>
       </c>
@@ -1303,8 +1321,11 @@
       <c r="N2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O2" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>160</v>
       </c>
@@ -1348,7 +1369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>143</v>
       </c>
@@ -1392,7 +1413,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>170</v>
       </c>
@@ -1436,7 +1457,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>174</v>
       </c>
@@ -1480,7 +1501,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>180</v>
       </c>
@@ -1524,7 +1545,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>181</v>
       </c>
@@ -1568,7 +1589,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>186</v>
       </c>
@@ -1612,7 +1633,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>188</v>
       </c>
@@ -1656,7 +1677,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>191</v>
       </c>
@@ -1700,7 +1721,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>196</v>
       </c>
@@ -1744,7 +1765,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>199</v>
       </c>
@@ -1788,7 +1809,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>202</v>
       </c>
@@ -1832,7 +1853,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>206</v>
       </c>
@@ -1876,7 +1897,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>211</v>
       </c>

--- a/FILTER.xlsx
+++ b/FILTER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SOFTWARE\GIT HUB\pdf-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B65BA9A-F326-4778-A281-78A59CA6B78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FAA2258-B0B6-4DCD-97DC-FDD74B410679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,372 +36,816 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="282">
+  <si>
+    <t>NXT II</t>
+  </si>
+  <si>
+    <t>GPX-CSII</t>
+  </si>
+  <si>
+    <t>GPX-CS</t>
+  </si>
+  <si>
+    <t>GPX-CL</t>
+  </si>
+  <si>
+    <t>GPX-CII</t>
+  </si>
+  <si>
+    <t>Flexa</t>
+  </si>
+  <si>
+    <t>Fujitrax</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>NXTR</t>
+  </si>
+  <si>
+    <t>GPX</t>
+  </si>
+  <si>
+    <t>Feeder</t>
+  </si>
+  <si>
+    <t>AIMEXIII</t>
+  </si>
+  <si>
+    <t>Nexim</t>
+  </si>
+  <si>
+    <t>NXTIII</t>
+  </si>
+  <si>
+    <t>KNOWLEDGE</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT II;NXT IIc;NXT;NXTR;AIM</t>
+  </si>
+  <si>
+    <t>GPX-CII;GPX-CSII;GPX-CL</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;NXT-H;NXTP;AIMEXR;Fuji Flexa;Fujitrax;Nexim</t>
+  </si>
+  <si>
+    <t>NXTR;Feeder</t>
+  </si>
   <si>
     <t>AIMEX III;AIMEX IIIc;NXT III;NXT IIIc;NXT-H</t>
   </si>
   <si>
+    <t>NXT II;NXT IIc</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXTR;NXTR PM;NXT-H;GPX;NXTP;AIMEXR;sFAB-D;sFAB-SH;sFAB-a;Nexim;FUJI Smart Factory;GPX-CII;GPX-CSII;Unit;GPX-HD;GPX-C;GPX-CS;GPX-CL</t>
+  </si>
+  <si>
+    <t>GPX-C;GPX-CS;GPX-CL</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;NXT-H;NXTP;Fuji Flexa;Fujitrax;Nexim</t>
+  </si>
+  <si>
+    <t>FUJITRAX</t>
+  </si>
+  <si>
+    <t>NXTR;Unit</t>
+  </si>
+  <si>
+    <t>NXTR;AIMEXR</t>
+  </si>
+  <si>
     <t>AIMEX III;AIMEX IIIc;NXT III;NXT IIIc</t>
   </si>
   <si>
+    <t>GPX-CII;GPX-CSII</t>
+  </si>
+  <si>
+    <t>GPX-C;GPX-CS</t>
+  </si>
+  <si>
+    <t>Fuji Flexa;Fujitrax;Nexim</t>
+  </si>
+  <si>
+    <t>sFAB-D;sFAB-SH;Feeder;sFAB50</t>
+  </si>
+  <si>
     <t>AIMEX III;AIMEX IIIc;NXT III;NXT IIIc;NXTR;AIMEXR</t>
   </si>
   <si>
+    <t>Nexim;FUJI Smart Factory</t>
+  </si>
+  <si>
+    <t>AIMEX;NXT II;NXT IIc;NXT;NXTP;XPF;XP;AIM;Unit;GPX-HD</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H;GPX;NXTP;AIM;GPX-HD;GPX-C;GPX-CS</t>
+  </si>
+  <si>
+    <t>Fuji Flexa;Fujitrax</t>
+  </si>
+  <si>
+    <t>NXTR;NXTR PM;Unit</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;NXT-H;NXT-Hw;GPX;GP;NXTP;sFAB-D;sFAB-SH;sFAB-a;XPF;Fuji Flexa;Fujitrax;Feeder;Nexim;FUJI Smart Factory;sTower II;XP;AIM;CP;F4G;FIP;Fuji Cam;GL;MCS;NP;QP;GPX-CII;GPX-CSII;Unit;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
+  </si>
+  <si>
     <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc</t>
   </si>
   <si>
-    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXTR;NXTR PM;NXT-H;GPX;NXTP;AIMEXR;sFAB-D;sFAB-SH;sFAB-a;Nexim;FUJI Smart Factory;GPX-CII;GPX-CSII;Unit;GPX-HD;GPX-C;GPX-CS;GPX-CL</t>
+    <t>NXTR;NXTR PM;AIMEXR;Nexim</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX II;AIMEX IIS;NXT II;NXT IIc;NXTP</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXTR;NXTR PM;GPX;NXTP;AIMEXR;sFAB-D;sFAB-SH;sFAB-a;Nexim;FUJI Smart Factory;GPX-CII;GPX-CSII;GPX-HD;GPX-C;GPX-CS</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXTR;NXTR PM;sFAB-D;Nexim;GPX-C;GPX-CS</t>
+  </si>
+  <si>
+    <t>GPX-CII;GPX-CSII;GPX-C;GPX-CS;GPX-CL</t>
+  </si>
+  <si>
+    <t>Fuji Flexa</t>
+  </si>
+  <si>
+    <t>NXTR;NXTR PM;AIMEXR;Unit</t>
+  </si>
+  <si>
+    <t>NXTR;NXTR PM;AIMEXR</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;NXT-H;NXT-Hw;GPX;GP;NXTP;XPF;Feeder;FUJI Smart Factory;sTower II;XP;AIM;CP;FIP;GL;NP;QP;GPX-CII;GPX-CSII;Unit;GPX-HD;GPX-C;GPX-CS;GPX-CL</t>
+  </si>
+  <si>
+    <t>AIMEX III</t>
+  </si>
+  <si>
+    <t>AIMEX II;AIMEX IIS;NXT II;NXT IIc;NXTP</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXTR;NXTR PM;NXT-H;NXT-Hw;NXTP;sFAB-D;sFAB-SH;sFAB-a;XPF;Nexim;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXTR;NXTR PM;NXT-H;NXT-Hw;NXTP;sFAB-D;sFAB-SH;sFAB-a;XPF;Nexim;FUJI Smart Factory;GPX-CII;GPX-CSII;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H;NXTP;Fuji Flexa;Fujitrax;Nexim</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT-H;GPX;NXTP;Unit;GPX-HD</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;NXT-H;NXT-Hw;GPX;GP;NXTP;sFAB-D;XPF;Feeder;XP;AIM;FIP;GL;NP;QP;Unit;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
+  </si>
+  <si>
+    <t>AIMEX III;NXT III;NXTR;Nexim</t>
   </si>
   <si>
     <t>NXT III;NXT IIIc;NXT II;NXT IIc</t>
   </si>
   <si>
+    <t>AIMEX;NXT II;NXT IIc</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXTR;NXTR PM;sFAB-D;sFAB-SH;Nexim;FUJI Smart Factory;GPX-CII;GPX-CSII</t>
+  </si>
+  <si>
+    <t>AIMEX;NXT;NXTR;NXTR PM;NXT-H;NXTP;sFAB-D;sFAB-SH;sFAB-a;XPF;Nexim;GPX-HD;GPX-C;GPX-CS;GPX-CL</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXTR;NXTR PM;NXT-H;NXT-Hw;NXTP;sFAB-D;sFAB-SH;sFAB-a;XPF;Nexim;GPX-CII;GPX-CSII;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
+  </si>
+  <si>
+    <t>Fujitrax;Nexim</t>
+  </si>
+  <si>
+    <t>NXT III;NXT IIIc;Unit</t>
+  </si>
+  <si>
+    <t>GPX-C</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H;NXT-Hw;GPX;GP;NXTP;sFAB-D;sFAB-a;XPF;Feeder;XP;AIM;CP;FIP;GL;NP;QP;Unit;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS</t>
+  </si>
+  <si>
     <t>NXT III;NXT IIIc</t>
   </si>
   <si>
+    <t>NXT II;NXT IIc;NXT</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXTR;NXTR PM;AIMEXR;sFAB-D;sFAB-SH;sFAB-a;Nexim;FUJI Smart Factory;GPX-CII;GPX-CSII</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXTR;NXTR PM;NXT-H;NXTP;sFAB-D;sFAB-SH;sFAB-a;XPF;Nexim;GPX-HD;GPX-C;GPX-CS;GPX-CL</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H;NXTP;Fuji Flexa;Fujitrax</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXTR;NXTR PM;NXT-H;GPX;AIMEXR;sFAB-D;sFAB-SH;Nexim;FUJI Smart Factory;Unit</t>
+  </si>
+  <si>
+    <t>NXT III;NXT IIIc;NXTR</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H;NXT-Hw;GPX;GP;NXTP;XPF;Feeder;XP;AIM;CP;FIP;GL;NP;QP;Unit;GPX-HD;GPX-C;GPX-CS;sFAB50</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIIc;AIMEX IIS</t>
+  </si>
+  <si>
     <t>NXT III;NXT IIIc;NXT II;NXT</t>
   </si>
   <si>
-    <t>NXT III;NXT IIIc;NXTR</t>
+    <t>AIMEX;AIMEX II;AIMEX IIS;NXT II;NXT IIc;NXT</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;AIMEXR;NXT III;NXT IIIc;NXT II;NXT IIc;NXTR;NXTR PM;sFAB-D;sFAB-SH;sFAB-a;Nexim;FUJI Smart Factory;GPX-CII;GPX-CSII</t>
+  </si>
+  <si>
+    <t>Fuji Flexa;Nexim</t>
   </si>
   <si>
     <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;AIM</t>
   </si>
   <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;NXT-H;NXT-Hw;GPX;GP;NXTP;sFAB-D;sFAB-SH;sFAB-a;XPF;Feeder;sTower II;XP;AIM;CP;FIP;GL;NP;QP;GPX-CII;GPX-CSII;Unit;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIIc</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX IIS;NXT II;NXT IIc;NXT;GPX</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;NXT-H;NXT-Hw;NXTP;sFAB-D;sFAB-SH;sFAB-a;XPF;Nexim;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
+  </si>
+  <si>
+    <t>sFAB-D;sFAB-SH;Fuji Flexa;Nexim;sFAB50</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;NXT-H;NXT-Hw;GPX;NXTP;sFAB-D;sFAB-SH;sFAB-a;XPF;Fuji Flexa;Fujitrax;Nexim;sTower II;XP;AIM;GPX-CII;GPX-CSII;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
+  </si>
+  <si>
+    <t>NXTR;NXTR PM;Heads;Unit</t>
+  </si>
+  <si>
+    <t>Feeder;Unit</t>
+  </si>
+  <si>
+    <t>NEXIM NOTE</t>
+  </si>
+  <si>
+    <t>NXT IIc</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;NXT-H;NXT-Hw;NXTP;sFAB-a;XPF;Nexim;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;NXT-H;NXT-Hw;GPX;NXTP;sFAB-D;sFAB-SH;sFAB-a;XPF;sTower II;AIM;SW-BA;GPX-CII;GPX-CSII;Unit;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;NXT-H;NXT-Hw;GPX;GP;NXTP;sFAB-D;sFAB-SH;sFAB-a;XPF;Fuji Flexa;Fujitrax;sTower II;XP;AIM;CP;FIP;GL;NP;QP;GPX-CII;GPX-CSII;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
+  </si>
+  <si>
+    <t>NXT III;NXT IIIc;NXT-H;NXT-Hw;Unit</t>
+  </si>
+  <si>
     <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR</t>
   </si>
   <si>
+    <t>GPX-CW</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;NXT-H;NXT-Hw;GPX;NXTP;sFAB-D;sFAB-SH;sFAB-a;XPF;Fuji Flexa;Fujitrax;Feeder;Nexim;FUJI Smart Factory;sTower II;XP;AIM;CP;F4G;FIP;Fuji Cam;GL;MCS;NP;QP;GPX-CII;GPX-CSII;Unit;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
+  </si>
+  <si>
+    <t>NEXIM UPGRADE NOTE IMAGE</t>
+  </si>
+  <si>
+    <t>NXT II;NXT</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H;NXT-Hw;NXTP;sFAB-D;sFAB-a;XPF;Nexim;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR PM;NXT-H;NXT-Hw;NXTP;sFAB-D;XPF;Fuji Flexa;Nexim;sTower II;Unit;GPX-C;GPX-CS;sFAB50</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;NXT-H;NXT-Hw;GPX;GP;NXTP;sFAB-D;sFAB-SH;sFAB-a;XPF;Fuji Flexa;Fujitrax;Nexim;sTower II;XP;AIM;CP;F4G;FIP;Fuji Cam;GL;MCS;NP;QP;GPX-CII;GPX-CSII;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
+  </si>
+  <si>
     <t>AIMEX;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR</t>
   </si>
   <si>
+    <t>GPX;Fujitrax;Feeder</t>
+  </si>
+  <si>
+    <t>NEXIM UPGRADE NOTE PDF</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX II;NXT II;NXT IIc;NXT;AIM</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;NXT-H;NXT-Hw;NXTP;sFAB-D;sFAB-a;XPF;Nexim;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
+  </si>
+  <si>
+    <t>sFAB-D;Fuji Flexa;Nexim;sFAB50</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX II;AIMEX IIS;NXT II;NXT IIc;NXT;NXTP;XPF;Fuji Flexa;Fujitrax;AIM</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXTR;AIMEXR;FUJI Smart Factory</t>
+  </si>
+  <si>
+    <t>NXT;Feeder;XP;CP;QP</t>
+  </si>
+  <si>
     <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;FUJI Smart Factory</t>
   </si>
   <si>
-    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXTR;AIMEXR;FUJI Smart Factory</t>
+    <t>AIMEX;AIMEX IIS;NXT II;NXT IIc;NXT;XPF;AIM</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;NXT-H;NXT-Hw;NXTP;sFAB-D;XPF;Nexim;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
+  </si>
+  <si>
+    <t>Fuji Flexa;sFAB50</t>
+  </si>
+  <si>
+    <t>AIMEX;Fuji Flexa;Fujitrax</t>
+  </si>
+  <si>
+    <t>NXTR PM</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;GPX;NXTP;XPF;GPX-HD</t>
+  </si>
+  <si>
+    <t>Feeder;QP</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX II;AIMEX IIS;NXT II;NXT IIc;NXT;XPF;AIM</t>
+  </si>
+  <si>
+    <t>AIMEX;NXT II;NXT IIc;NXT;GPX;XPF;Fuji Flexa;Fujitrax;Unit</t>
+  </si>
+  <si>
+    <t>NXTR;NXTR PM</t>
   </si>
   <si>
     <t>AIMEX III;AIMEX IIIc;NXT III;NXT IIIc;NXTR</t>
   </si>
   <si>
+    <t>AIMEX;AIMEX IIS;NXT II;NXT IIc;NXT;AIM</t>
+  </si>
+  <si>
+    <t>AIMEX;NXT II;NXT IIc;NXT;Fuji Flexa;Fujitrax</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;Unit</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;AIMEXR;AIM</t>
+  </si>
+  <si>
     <t>NXT III</t>
   </si>
   <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;AIMEXR;AIM</t>
+    <t>AIMEX;AIMEX IIS;NXT II;NXT IIc;NXT;AIM;Unit</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H;NXT-Hw;NXTP;sFAB-D;Nexim;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
+  </si>
+  <si>
+    <t>AIMEX;NXT II;NXT IIc;NXT;Fuji Flexa;Fujitrax;AIM</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXTR;Unit</t>
   </si>
   <si>
     <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXTR</t>
   </si>
   <si>
+    <t>AIMEX;AIMEX II;AIMEX IIS;NXT II;NXT IIc;NXT;AIM</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H;NXT-Hw;GPX;NXTP;XPF;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
+  </si>
+  <si>
+    <t>AIMEX;NXT II;NXT;XPF;Fujitrax</t>
+  </si>
+  <si>
+    <t>GPX;GPX-HD</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;NXT-H;NXT-Hw;GPX;GP;NXTP;sFAB-D;sFAB-SH;sFAB-a;XPF;sTower II;XP;AIM;CP;FIP;GL;NP;QP;GPX-CII;GPX-CSII;Unit;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
+  </si>
+  <si>
+    <t>AIMEX;NXT II;NXT;Fuji Flexa;Fujitrax;AIM</t>
+  </si>
+  <si>
     <t>NXT III;NXT IIIc;NXT II;NXT IIc;NXT</t>
   </si>
   <si>
-    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc</t>
-  </si>
-  <si>
-    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;NXT-H;NXTP;AIMEXR;Fuji Flexa;Fujitrax;Nexim</t>
+    <t>AIMEX;NXT II;NXT IIc;NXT;XPF;AIM</t>
+  </si>
+  <si>
+    <t>GPX_C;GPX_CS;GPX_CL;</t>
+  </si>
+  <si>
+    <t>Fuji Flexa;Fujitrax;Unit</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT-H;Unit</t>
   </si>
   <si>
     <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;NXT III;NXT IIIc;NXT II;NXT IIc;NXT-H</t>
   </si>
   <si>
-    <t>AIMEX III;NXT III;NXTR;Nexim</t>
+    <t>AIMEX;NXT II;NXT IIc;NXT;AIM</t>
+  </si>
+  <si>
+    <t>GPX_CII;GPX_CSII;</t>
+  </si>
+  <si>
+    <t>NXT;GPX;Fuji Flexa;Fujitrax;AIM;Unit</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT IIIc;NXT II;NXT;Unit</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX IIS;NXT II;NXT IIc</t>
+  </si>
+  <si>
+    <t>GPX_CII;GPX_CSII;GPX_CL;</t>
   </si>
   <si>
     <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H;NXT-Hw;AIM</t>
   </si>
   <si>
+    <t>NEXIM LOG</t>
+  </si>
+  <si>
+    <t>AIMEX;NXT II;NXT IIc;XPF</t>
+  </si>
+  <si>
+    <t>Fuji Flexa;Unit</t>
+  </si>
+  <si>
+    <t>NXT;Fuji Flexa;Fujitrax;AIM</t>
+  </si>
+  <si>
+    <t>NXT IIIc;NXT II;Unit</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXTR;AIMEXR</t>
+  </si>
+  <si>
+    <t>GPX-HD</t>
+  </si>
+  <si>
+    <t>NXT II;Unit</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H;GPX;NXTP;sFAB-D;XPF;XP;Unit;sFAB50</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXTR</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXTR;Nexim</t>
+  </si>
+  <si>
+    <t>NXT;Fuji Flexa;Fujitrax;AIM;Unit</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIIc;NXT-H;NXT-Hw;Unit</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;AIMEXR</t>
+  </si>
+  <si>
+    <t>sFAB-D;sFAB-SH;Nexim;sFAB50</t>
+  </si>
+  <si>
     <t>NXT III;NXT II;NXT</t>
   </si>
   <si>
-    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXTR;AIMEXR</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXTR</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;AIMEXR</t>
+    <t>AIMEX;NXT II;NXT IIc;NXT</t>
+  </si>
+  <si>
+    <t>NXT;Fuji Flexa;XP</t>
+  </si>
+  <si>
+    <t>NXT;Fuji Flexa;Fujitrax;MCS;Unit</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX II;AIMEX IIS;NXT III;NXT II;NXT IIc;NXT;AIM;Unit</t>
   </si>
   <si>
     <t>AIMEX III;AIMEX IIIc;AIMEX IIS;NXT III;NXT IIIc</t>
   </si>
   <si>
-    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXTR;NXTR PM;GPX;NXTP;AIMEXR;sFAB-D;sFAB-SH;sFAB-a;Nexim;FUJI Smart Factory;GPX-CII;GPX-CSII;GPX-HD;GPX-C;GPX-CS</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;GPX;NXTP;XPF;GPX-HD</t>
+    <t>NXT II;NXT IIc;NXT;XPF;AIM</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX II;AIMEX IIS;GPX;NXTP;XPF;XP;Unit</t>
+  </si>
+  <si>
+    <t>NXTR;Heads</t>
+  </si>
+  <si>
+    <t>AIMEX;NXT II;NXT;AIM</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;XPF;XP;AIM;Unit</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX II;AIMEX IIS</t>
+  </si>
+  <si>
+    <t>NXT II;NXT IIc;NXTP</t>
+  </si>
+  <si>
+    <t>GPX_CL</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;AIMEXR;sFAB-D;sFAB-SH;sFAB-a;sFAB50</t>
   </si>
   <si>
     <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc</t>
   </si>
   <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT-H;GPX;NXTP;Unit;GPX-HD</t>
+    <t>AIMEX;NXT II;NXT IIc;NXTP</t>
+  </si>
+  <si>
+    <t>GPX CL</t>
+  </si>
+  <si>
+    <t>Fuji Flexa;XP</t>
+  </si>
+  <si>
+    <t>GPX_CL;</t>
   </si>
   <si>
     <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT II;NXT IIc;NXT;AIM</t>
   </si>
   <si>
-    <t>NXT III;NXT IIIc;Unit</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;AIMEXR;sFAB-D;sFAB-SH;sFAB-a;sFAB50</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXTR;NXTR PM;NXT-H;GPX;AIMEXR;sFAB-D;sFAB-SH;Nexim;FUJI Smart Factory;Unit</t>
+    <t>NXT II;NXT;AIM</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIIc;NXT III;NXT IIIc;NXTR PM</t>
+  </si>
+  <si>
+    <t>AIMEX IIIc</t>
+  </si>
+  <si>
+    <t>AIMEX;NXT II;NXT;XPF;AIM</t>
+  </si>
+  <si>
+    <t>AIMEX;NXT II;NXT IIc;NXT;AIM;Unit</t>
+  </si>
+  <si>
+    <t>NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H;NXTP;sFAB-D;sFAB-SH;XPF;XP;GPX-HD;sFAB50</t>
+  </si>
+  <si>
+    <t>AIMEX;NXT II</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;sFAB-D;sFAB-SH;sFAB50</t>
   </si>
   <si>
     <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT</t>
   </si>
   <si>
+    <t>AIMEX III;AIMEX IIIc;Nexim</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;AIMEXR</t>
+  </si>
+  <si>
+    <t>NXT II;NXT IIc;NXT;AIM</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;GPX;NXTP;XPF</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIIc;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT-H;NXT-Hw</t>
+  </si>
+  <si>
+    <t>AIMEX;NXT II;NXT</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIIc;NXT III;NXT IIIc;NXT-H;NXT-Hw</t>
+  </si>
+  <si>
+    <t>AIMEX;NXT II;NXT;GP;XPF;XP;AIM;CP;FIP;GL;NP;QP</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT-H;NXT-Hw;Heads</t>
+  </si>
+  <si>
     <t>NXT IIIc</t>
   </si>
   <si>
-    <t>AIMEX III;AIMEX IIIc;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT-H;NXT-Hw</t>
-  </si>
-  <si>
-    <t>AIMEX III;AIMEX IIIc;NXT III;NXT IIIc;NXT-H;NXT-Hw</t>
-  </si>
-  <si>
-    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT-H;NXT-Hw;Heads</t>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT-H;NXT-Hw</t>
+  </si>
+  <si>
+    <t>sFAB-D;Nexim;sFAB50</t>
+  </si>
+  <si>
+    <t>AIMEX;NXT II;NXT IIc;NXT;XPF</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIIc;AIMEX IIS;NXT III;NXT IIIc;NXTR</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS</t>
+  </si>
+  <si>
+    <t>AIMEX;NXT II;NXT;GPX;XPF</t>
   </si>
   <si>
     <t>AIMEX II;NXT III;NXT IIIc;NXT II;NXT IIc</t>
   </si>
   <si>
+    <t>NXT II;NXT;XPF;AIM</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H;AIM</t>
+  </si>
+  <si>
+    <t>NEXIM</t>
+  </si>
+  <si>
     <t>AIMEX;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT</t>
   </si>
   <si>
+    <t>NXT II;NXT;XPF;XP;AIM;CP</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIIc;NXT III;NXT IIIc;NXTR;NXTR PM;sFAB-D</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;AIM</t>
+  </si>
+  <si>
     <t>AIMEX;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc</t>
   </si>
   <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT-H;NXT-Hw</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXTR;NXTR PM;sFAB-D;sFAB-SH;Nexim;FUJI Smart Factory;GPX-CII;GPX-CSII</t>
-  </si>
-  <si>
-    <t>AIMEX III;AIMEX IIIc;NXT III;NXT IIIc;NXTR PM</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H;AIM</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;AIM</t>
+    <t>AIMEX III;AIMEX IIIc;NXT III;NXT IIIc;NXT-H;NXTP;sFAB-D;GPX-C</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIIc;NXT-H;NXT-Hw</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H;NXT-Hw;GPX;NXTP;sFAB-D;sFAB-SH;sFAB-a;XPF;XP;AIM;sFAB50</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIIc;NXT III;NXT IIIc;NXT-H;NXT-Hw;GPX;NXTP;sFAB-D</t>
   </si>
   <si>
     <t>NXT III;NXT IIIc;NXT II;NXT IIc;NXT;AIM</t>
   </si>
   <si>
-    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;NXT-H;NXTP;Fuji Flexa;Fujitrax;Nexim</t>
+    <t>AIMEX III;AIMEX IIIc;NXT III;NXT IIIc;NXT-H;NXT-Hw;NXTP;sFAB-D;GPX-HD</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;XPF;XP;AIM</t>
   </si>
   <si>
     <t>NXT III;NXT IIIc;NXT II</t>
   </si>
   <si>
-    <t>NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;sFAB-D;sFAB-SH;sFAB50</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXTR;NXTR PM;AIMEXR;sFAB-D;sFAB-SH;sFAB-a;Nexim;FUJI Smart Factory;GPX-CII;GPX-CSII</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;AIMEXR;NXT III;NXT IIIc;NXT II;NXT IIc;NXTR;NXTR PM;sFAB-D;sFAB-SH;sFAB-a;Nexim;FUJI Smart Factory;GPX-CII;GPX-CSII</t>
-  </si>
-  <si>
-    <t>NXT III;NXT IIIc;NXT-H;NXT-Hw;Unit</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXTR;NXTR PM;NXT-H;NXT-Hw;NXTP;sFAB-D;sFAB-SH;sFAB-a;XPF;Nexim;FUJI Smart Factory;GPX-CII;GPX-CSII;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;XPF;XP;AIM</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H;GPX;NXTP;AIM;GPX-HD;GPX-C;GPX-CS</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXTR;NXTR PM;NXT-H;NXT-Hw;NXTP;sFAB-D;sFAB-SH;sFAB-a;XPF;Nexim;GPX-CII;GPX-CSII;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
-  </si>
-  <si>
-    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H;NXTP;Fuji Flexa;Fujitrax;Nexim</t>
-  </si>
-  <si>
-    <t>AIMEX III;AIMEX IIIc;AIMEX IIS;NXT III;NXT IIIc;NXTR</t>
-  </si>
-  <si>
-    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXTR;NXTR PM;sFAB-D;Nexim;GPX-C;GPX-CS</t>
+    <t>NXT;GPX;GP;XPF;XP;AIM;CP;FIP;GL;NP;QP</t>
   </si>
   <si>
     <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;FUJI Smart Factory</t>
   </si>
   <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXTR;NXTR PM;NXT-H;NXT-Hw;NXTP;sFAB-D;sFAB-SH;sFAB-a;XPF;Nexim;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
-  </si>
-  <si>
-    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXTR;Nexim</t>
-  </si>
-  <si>
-    <t>AIMEX III;AIMEX IIIc;NXT III;NXT IIIc;NXTR;NXTR PM;sFAB-D</t>
-  </si>
-  <si>
     <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc</t>
   </si>
   <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;NXT-H;NXT-Hw;GPX;GP;NXTP;sFAB-D;sFAB-SH;sFAB-a;XPF;Fuji Flexa;Fujitrax;Feeder;Nexim;FUJI Smart Factory;sTower II;XP;AIM;CP;F4G;FIP;Fuji Cam;GL;MCS;NP;QP;GPX-CII;GPX-CSII;Unit;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
+    <t>NXTR_S;NXTR_A;AIMEXR;</t>
+  </si>
+  <si>
+    <t>NXT;GPX;AIM</t>
   </si>
   <si>
     <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;XPF;AIM</t>
   </si>
   <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;NXT-H;NXT-Hw;GPX;NXTP;sFAB-D;sFAB-SH;sFAB-a;XPF;sTower II;AIM;SW-BA;GPX-CII;GPX-CSII;Unit;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXTR;NXTR PM;NXT-H;NXTP;sFAB-D;sFAB-SH;sFAB-a;XPF;Nexim;GPX-HD;GPX-C;GPX-CS;GPX-CL</t>
+    <t>NXTR_S;NXTR_A;AIMEXR;NXT_III;NXT_IIIc;NXT_II;NXT_IIc;NXT;AIMEX_III;AIMEX_IIIc;AIMEX_II;AIMEX_IIS;AIMEX;</t>
+  </si>
+  <si>
+    <t>NXTR_S;NXTR_A;</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H</t>
   </si>
   <si>
     <t>NXT III;NXT II;NXT IIc</t>
   </si>
   <si>
-    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H;NXTP;Fuji Flexa;Fujitrax</t>
-  </si>
-  <si>
-    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III</t>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;sFAB-D;sFAB50</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXTP</t>
   </si>
   <si>
     <t>NXT III;NXT II</t>
   </si>
   <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;NXT-H;NXT-Hw;GPX;GP;NXTP;XPF;Feeder;FUJI Smart Factory;sTower II;XP;AIM;CP;FIP;GL;NP;QP;GPX-CII;GPX-CSII;Unit;GPX-HD;GPX-C;GPX-CS;GPX-CL</t>
-  </si>
-  <si>
-    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H;NXTP;sFAB-D;sFAB-SH;XPF;XP;GPX-HD;sFAB50</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;NXT-H;NXT-Hw;GPX;GP;NXTP;sFAB-D;XPF;Feeder;XP;AIM;FIP;GL;NP;QP;Unit;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;NXT-H;NXT-Hw;NXTP;sFAB-D;sFAB-SH;sFAB-a;XPF;Nexim;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;Unit</t>
+    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;sFAB-D;sFAB50</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT-H;NXT-Hw</t>
   </si>
   <si>
     <t>AIMEX;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;XPF;AIM</t>
   </si>
   <si>
-    <t>AIMEX;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;GPX;NXTP;XPF</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H</t>
+    <t>AIMEX;AIMEX III;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;XPF</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT-H;NXT-Hw</t>
   </si>
   <si>
     <t>AIMEX;AIMEX II;NXT III;NXT IIIc;NXT II;NXT IIc;NXT</t>
   </si>
   <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;NXT-H;NXT-Hw;NXTP;sFAB-a;XPF;Nexim;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;sFAB-D;sFAB50</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H;NXT-Hw;NXTP;sFAB-D;sFAB-a;XPF;Nexim;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H;NXT-Hw</t>
   </si>
   <si>
     <t>NXT III;NXT IIIc;NXT IIc</t>
   </si>
   <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXTP</t>
-  </si>
-  <si>
-    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;sFAB-D;sFAB50</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;NXT-H;NXT-Hw;NXTP;sFAB-D;sFAB-a;XPF;Nexim;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT-H;NXT-Hw</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;NXT-H;NXT-Hw;NXTP;sFAB-D;XPF;Nexim;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXTR;Unit</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;XPF</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;NXT-H;NXT-Hw;GPX;NXTP;sFAB-D;sFAB-SH;sFAB-a;XPF;Fuji Flexa;Fujitrax;Nexim;sTower II;XP;AIM;GPX-CII;GPX-CSII;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
-  </si>
-  <si>
-    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT-H;NXT-Hw</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR PM;NXT-H;NXT-Hw;NXTP;sFAB-D;XPF;Fuji Flexa;Nexim;sTower II;Unit;GPX-C;GPX-CS;sFAB50</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H;NXT-Hw</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H;NXT-Hw;GPX;GP;NXTP;sFAB-D;sFAB-a;XPF;Feeder;XP;AIM;CP;FIP;GL;NP;QP;Unit;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
+    <t>AIMEX;AIMEX III;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H;NXT-Hw</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT-H</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIIc;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIIc;AIMEX IIS;NXT III;NXT IIIc;sFAB50</t>
   </si>
   <si>
     <t>AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT-H;sFAB-D;XPF;sFAB50</t>
   </si>
   <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H;NXT-Hw;NXTP;sFAB-D;Nexim;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
+    <t>AIMEX III;AIMEX IIIc;NXT III;NXT IIIc;NXT-H;NXT-Hw;NXTP</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;XPF;XP;CP</t>
   </si>
   <si>
     <t>AIMEX;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H;NXT-Hw;AIM</t>
   </si>
   <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H;NXT-Hw;GPX;NXTP;XPF;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H;NXT-Hw</t>
-  </si>
-  <si>
-    <t>AIMEX III;AIMEX IIIc;NXT III;NXT IIIc;NXT-H;NXTP;sFAB-D;GPX-C</t>
-  </si>
-  <si>
-    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT-H</t>
-  </si>
-  <si>
-    <t>AIMEX III;AIMEX IIIc;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT</t>
-  </si>
-  <si>
-    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT-H;Unit</t>
-  </si>
-  <si>
-    <t>AIMEX III;AIMEX IIIc;AIMEX IIS;NXT III;NXT IIIc;sFAB50</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT IIIc;NXT II;NXT;Unit</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H;NXT-Hw;GPX;GP;NXTP;XPF;Feeder;XP;AIM;CP;FIP;GL;NP;QP;Unit;GPX-HD;GPX-C;GPX-CS;sFAB50</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H;NXT-Hw;GPX;NXTP;sFAB-D;sFAB-SH;sFAB-a;XPF;XP;AIM;sFAB50</t>
-  </si>
-  <si>
-    <t>AIMEX III;AIMEX IIIc;NXT III;NXT IIIc;NXT-H;NXT-Hw;GPX;NXTP;sFAB-D</t>
-  </si>
-  <si>
-    <t>AIMEX III;AIMEX IIIc;NXT III;NXT IIIc;NXT-H;NXT-Hw;NXTP;sFAB-D;GPX-HD</t>
-  </si>
-  <si>
-    <t>AIMEX III;AIMEX IIIc;NXT III;NXT IIIc;NXT-H;NXT-Hw;NXTP</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;XPF;XP;CP</t>
-  </si>
-  <si>
-    <t>NXT IIIc;NXT II;Unit</t>
+    <t>AIMEX III;AIMEX IIIc;NXT-H</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX II</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIIc;AIMEX II</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;AIM</t>
+  </si>
+  <si>
+    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H;NXT-Hw;NXTP;XPF;XP;AIM</t>
+  </si>
+  <si>
+    <t>AIMEX III;AIMEX IIS</t>
   </si>
   <si>
     <t>AIMEX;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;AIM</t>
@@ -410,39 +854,21 @@
     <t>AIMEX;AIMEX II;AIMEX IIS;NXT III;NXT II;NXT IIc;NXTP</t>
   </si>
   <si>
-    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H;GPX;NXTP;sFAB-D;XPF;XP;Unit;sFAB50</t>
-  </si>
-  <si>
     <t>AIMEX;AIMEX II;AIMEX IIS;NXT III;NXT II;NXT IIc;NXT;AIM</t>
   </si>
   <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXT-H;NXT-Hw;NXTP;XPF;XP;AIM</t>
-  </si>
-  <si>
     <t>NXT IIIc;NXT IIc</t>
   </si>
   <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;NXT-H;NXT-Hw;GPX;GP;NXTP;sFAB-D;sFAB-SH;sFAB-a;XPF;Fuji Flexa;Fujitrax;sTower II;XP;AIM;CP;FIP;GL;NP;QP;GPX-CII;GPX-CSII;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;NXT-H;NXT-Hw;GPX;GP;NXTP;sFAB-D;sFAB-SH;sFAB-a;XPF;Fuji Flexa;Fujitrax;Nexim;sTower II;XP;AIM;CP;F4G;FIP;Fuji Cam;GL;MCS;NP;QP;GPX-CII;GPX-CSII;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
-  </si>
-  <si>
     <t>NXT III;NXT IIIc;NXT-H</t>
   </si>
   <si>
     <t>AIMEX II;AIMEX IIS;NXT III</t>
   </si>
   <si>
-    <t>AIMEX;AIMEX II;AIMEX IIS;NXT III;NXT II;NXT IIc;NXT;AIM;Unit</t>
-  </si>
-  <si>
     <t>AIMEX;AIMEX II;AIMEX IIS;NXT III;NXT II;NXT IIc</t>
   </si>
   <si>
-    <t>AIMEX;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;XPF;XP;AIM;Unit</t>
-  </si>
-  <si>
     <t>AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc</t>
   </si>
   <si>
@@ -456,432 +882,6 @@
   </si>
   <si>
     <t>NXT III;NXT II;NXT IIc;NXT</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;NXT-H;NXT-Hw;GPX;GP;NXTP;sFAB-D;sFAB-SH;sFAB-a;XPF;Feeder;sTower II;XP;AIM;CP;FIP;GL;NP;QP;GPX-CII;GPX-CSII;Unit;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;NXT-H;NXT-Hw;GPX;GP;NXTP;sFAB-D;sFAB-SH;sFAB-a;XPF;sTower II;XP;AIM;CP;FIP;GL;NP;QP;GPX-CII;GPX-CSII;Unit;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT III;NXT IIIc;NXT II;NXT IIc;NXT;NXTR;NXTR PM;NXT-H;NXT-Hw;GPX;NXTP;sFAB-D;sFAB-SH;sFAB-a;XPF;Fuji Flexa;Fujitrax;Feeder;Nexim;FUJI Smart Factory;sTower II;XP;AIM;CP;F4G;FIP;Fuji Cam;GL;MCS;NP;QP;GPX-CII;GPX-CSII;Unit;GPX-HD;GPX-C;GPX-CS;GPX-CL;sFAB50</t>
-  </si>
-  <si>
-    <t>NXT II</t>
-  </si>
-  <si>
-    <t>GPX-CSII</t>
-  </si>
-  <si>
-    <t>GPX-CS</t>
-  </si>
-  <si>
-    <t>GPX-CL</t>
-  </si>
-  <si>
-    <t>GPX-CII</t>
-  </si>
-  <si>
-    <t>Flexa</t>
-  </si>
-  <si>
-    <t>Fujitrax</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>NXTR</t>
-  </si>
-  <si>
-    <t>GPX</t>
-  </si>
-  <si>
-    <t>Feeder</t>
-  </si>
-  <si>
-    <t>AIMEXIII</t>
-  </si>
-  <si>
-    <t>Nexim</t>
-  </si>
-  <si>
-    <t>NXTIII</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;NXT II;NXT IIc;NXT;NXTR;AIM</t>
-  </si>
-  <si>
-    <t>GPX-CII;GPX-CSII;GPX-CL</t>
-  </si>
-  <si>
-    <t>NXTR;Feeder</t>
-  </si>
-  <si>
-    <t>NXT II;NXT IIc</t>
-  </si>
-  <si>
-    <t>GPX-C;GPX-CS;GPX-CL</t>
-  </si>
-  <si>
-    <t>FUJITRAX</t>
-  </si>
-  <si>
-    <t>NXTR;Unit</t>
-  </si>
-  <si>
-    <t>NXTR;AIMEXR</t>
-  </si>
-  <si>
-    <t>GPX-CII;GPX-CSII</t>
-  </si>
-  <si>
-    <t>GPX-C;GPX-CS</t>
-  </si>
-  <si>
-    <t>Fuji Flexa;Fujitrax;Nexim</t>
-  </si>
-  <si>
-    <t>sFAB-D;sFAB-SH;Feeder;sFAB50</t>
-  </si>
-  <si>
-    <t>Nexim;FUJI Smart Factory</t>
-  </si>
-  <si>
-    <t>AIMEX;NXT II;NXT IIc;NXT;NXTP;XPF;XP;AIM;Unit;GPX-HD</t>
-  </si>
-  <si>
-    <t>Fuji Flexa;Fujitrax</t>
-  </si>
-  <si>
-    <t>NXTR;NXTR PM;Unit</t>
-  </si>
-  <si>
-    <t>NXTR;NXTR PM;AIMEXR;Nexim</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX II;AIMEX IIS;NXT II;NXT IIc;NXTP</t>
-  </si>
-  <si>
-    <t>GPX-CII;GPX-CSII;GPX-C;GPX-CS;GPX-CL</t>
-  </si>
-  <si>
-    <t>Fuji Flexa</t>
-  </si>
-  <si>
-    <t>NXTR;NXTR PM;AIMEXR;Unit</t>
-  </si>
-  <si>
-    <t>NXTR;NXTR PM;AIMEXR</t>
-  </si>
-  <si>
-    <t>AIMEX III</t>
-  </si>
-  <si>
-    <t>AIMEX II;AIMEX IIS;NXT II;NXT IIc;NXTP</t>
-  </si>
-  <si>
-    <t>AIMEX;NXT II;NXT IIc</t>
-  </si>
-  <si>
-    <t>AIMEX;NXT;NXTR;NXTR PM;NXT-H;NXTP;sFAB-D;sFAB-SH;sFAB-a;XPF;Nexim;GPX-HD;GPX-C;GPX-CS;GPX-CL</t>
-  </si>
-  <si>
-    <t>Fujitrax;Nexim</t>
-  </si>
-  <si>
-    <t>GPX-C</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS</t>
-  </si>
-  <si>
-    <t>NXT II;NXT IIc;NXT</t>
-  </si>
-  <si>
-    <t>AIMEX III;AIMEX IIIc;AIMEX IIS</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX II;AIMEX IIS;NXT II;NXT IIc;NXT</t>
-  </si>
-  <si>
-    <t>Fuji Flexa;Nexim</t>
-  </si>
-  <si>
-    <t>AIMEX III;AIMEX IIIc</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX IIS;NXT II;NXT IIc;NXT;GPX</t>
-  </si>
-  <si>
-    <t>sFAB-D;sFAB-SH;Fuji Flexa;Nexim;sFAB50</t>
-  </si>
-  <si>
-    <t>NXTR;NXTR PM;Heads;Unit</t>
-  </si>
-  <si>
-    <t>Feeder;Unit</t>
-  </si>
-  <si>
-    <t>NEXIM NOTE</t>
-  </si>
-  <si>
-    <t>NXT IIc</t>
-  </si>
-  <si>
-    <t>GPX-CW</t>
-  </si>
-  <si>
-    <t>NEXIM UPGRADE NOTE IMAGE</t>
-  </si>
-  <si>
-    <t>NXT II;NXT</t>
-  </si>
-  <si>
-    <t>GPX;Fujitrax;Feeder</t>
-  </si>
-  <si>
-    <t>NEXIM UPGRADE NOTE PDF</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX II;NXT II;NXT IIc;NXT;AIM</t>
-  </si>
-  <si>
-    <t>sFAB-D;Fuji Flexa;Nexim;sFAB50</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX II;AIMEX IIS;NXT II;NXT IIc;NXT;NXTP;XPF;Fuji Flexa;Fujitrax;AIM</t>
-  </si>
-  <si>
-    <t>NXT;Feeder;XP;CP;QP</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX IIS;NXT II;NXT IIc;NXT;XPF;AIM</t>
-  </si>
-  <si>
-    <t>Fuji Flexa;sFAB50</t>
-  </si>
-  <si>
-    <t>AIMEX;Fuji Flexa;Fujitrax</t>
-  </si>
-  <si>
-    <t>NXTR PM</t>
-  </si>
-  <si>
-    <t>Feeder;QP</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX II;AIMEX IIS;NXT II;NXT IIc;NXT;XPF;AIM</t>
-  </si>
-  <si>
-    <t>AIMEX;NXT II;NXT IIc;NXT;GPX;XPF;Fuji Flexa;Fujitrax;Unit</t>
-  </si>
-  <si>
-    <t>NXTR;NXTR PM</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX IIS;NXT II;NXT IIc;NXT;AIM</t>
-  </si>
-  <si>
-    <t>AIMEX;NXT II;NXT IIc;NXT;Fuji Flexa;Fujitrax</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX IIS;NXT II;NXT IIc;NXT;AIM;Unit</t>
-  </si>
-  <si>
-    <t>AIMEX;NXT II;NXT IIc;NXT;Fuji Flexa;Fujitrax;AIM</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX II;AIMEX IIS;NXT II;NXT IIc;NXT;AIM</t>
-  </si>
-  <si>
-    <t>AIMEX;NXT II;NXT;XPF;Fujitrax</t>
-  </si>
-  <si>
-    <t>GPX;GPX-HD</t>
-  </si>
-  <si>
-    <t>AIMEX;NXT II;NXT;Fuji Flexa;Fujitrax;AIM</t>
-  </si>
-  <si>
-    <t>AIMEX;NXT II;NXT IIc;NXT;XPF;AIM</t>
-  </si>
-  <si>
-    <t>Fuji Flexa;Fujitrax;Unit</t>
-  </si>
-  <si>
-    <t>AIMEX;NXT II;NXT IIc;NXT;AIM</t>
-  </si>
-  <si>
-    <t>NXT;GPX;Fuji Flexa;Fujitrax;AIM;Unit</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX IIS;NXT II;NXT IIc</t>
-  </si>
-  <si>
-    <t>NEXIM LOG</t>
-  </si>
-  <si>
-    <t>AIMEX;NXT II;NXT IIc;XPF</t>
-  </si>
-  <si>
-    <t>Fuji Flexa;Unit</t>
-  </si>
-  <si>
-    <t>NXT;Fuji Flexa;Fujitrax;AIM</t>
-  </si>
-  <si>
-    <t>GPX-HD</t>
-  </si>
-  <si>
-    <t>NXT II;Unit</t>
-  </si>
-  <si>
-    <t>NXT;Fuji Flexa;Fujitrax;AIM;Unit</t>
-  </si>
-  <si>
-    <t>AIMEX III;AIMEX IIIc;NXT-H;NXT-Hw;Unit</t>
-  </si>
-  <si>
-    <t>sFAB-D;sFAB-SH;Nexim;sFAB50</t>
-  </si>
-  <si>
-    <t>AIMEX;NXT II;NXT IIc;NXT</t>
-  </si>
-  <si>
-    <t>NXT;Fuji Flexa;XP</t>
-  </si>
-  <si>
-    <t>NXT;Fuji Flexa;Fujitrax;MCS;Unit</t>
-  </si>
-  <si>
-    <t>NXT II;NXT IIc;NXT;XPF;AIM</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX II;AIMEX IIS;GPX;NXTP;XPF;XP;Unit</t>
-  </si>
-  <si>
-    <t>NXTR;Heads</t>
-  </si>
-  <si>
-    <t>AIMEX;NXT II;NXT;AIM</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX II;AIMEX IIS</t>
-  </si>
-  <si>
-    <t>NXT II;NXT IIc;NXTP</t>
-  </si>
-  <si>
-    <t>GPX_CL</t>
-  </si>
-  <si>
-    <t>AIMEX;NXT II;NXT IIc;NXTP</t>
-  </si>
-  <si>
-    <t>Fuji Flexa;XP</t>
-  </si>
-  <si>
-    <t>NXT II;NXT;AIM</t>
-  </si>
-  <si>
-    <t>AIMEX IIIc</t>
-  </si>
-  <si>
-    <t>AIMEX;NXT II;NXT;XPF;AIM</t>
-  </si>
-  <si>
-    <t>AIMEX;NXT II;NXT IIc;NXT;AIM;Unit</t>
-  </si>
-  <si>
-    <t>AIMEX;NXT II</t>
-  </si>
-  <si>
-    <t>AIMEX III;AIMEX IIIc;Nexim</t>
-  </si>
-  <si>
-    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;AIMEXR</t>
-  </si>
-  <si>
-    <t>NXT II;NXT IIc;NXT;AIM</t>
-  </si>
-  <si>
-    <t>AIMEX;NXT II;NXT</t>
-  </si>
-  <si>
-    <t>AIMEX;NXT II;NXT;GP;XPF;XP;AIM;CP;FIP;GL;NP;QP</t>
-  </si>
-  <si>
-    <t>sFAB-D;Nexim;sFAB50</t>
-  </si>
-  <si>
-    <t>AIMEX;NXT II;NXT IIc;NXT;XPF</t>
-  </si>
-  <si>
-    <t>AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS</t>
-  </si>
-  <si>
-    <t>AIMEX;NXT II;NXT;GPX;XPF</t>
-  </si>
-  <si>
-    <t>NXT II;NXT;XPF;AIM</t>
-  </si>
-  <si>
-    <t>NXT II;NXT;XPF;XP;AIM;CP</t>
-  </si>
-  <si>
-    <t>AIMEX III;AIMEX IIIc;NXT-H;NXT-Hw</t>
-  </si>
-  <si>
-    <t>NXT;GPX;GP;XPF;XP;AIM;CP;FIP;GL;NP;QP</t>
-  </si>
-  <si>
-    <t>NXTR_S;NXTR_A;AIMEXR;</t>
-  </si>
-  <si>
-    <t>NXT;GPX;AIM</t>
-  </si>
-  <si>
-    <t>AIMEX III;AIMEX IIIc;NXT-H</t>
-  </si>
-  <si>
-    <t>AIMEX III;AIMEX II</t>
-  </si>
-  <si>
-    <t>AIMEX III;AIMEX IIIc;AIMEX II</t>
-  </si>
-  <si>
-    <t>AIMEX;AIMEX III;AIMEX IIIc;AIMEX II;AIMEX IIS;AIM</t>
-  </si>
-  <si>
-    <t>AIMEX III;AIMEX IIS</t>
-  </si>
-  <si>
-    <t>GPX CL</t>
-  </si>
-  <si>
-    <t>GPX_CII;GPX_CSII;</t>
-  </si>
-  <si>
-    <t>GPX_CL;</t>
-  </si>
-  <si>
-    <t>NEXIM</t>
-  </si>
-  <si>
-    <t>NXTR_S;NXTR_A;AIMEXR;NXT_III;NXT_IIIc;NXT_II;NXT_IIc;NXT;AIMEX_III;AIMEX_IIIc;AIMEX_II;AIMEX_IIS;AIMEX;</t>
-  </si>
-  <si>
-    <t>NXTR_S;NXTR_A;</t>
-  </si>
-  <si>
-    <t>GPX_CII;GPX_CSII;GPX_CL;</t>
-  </si>
-  <si>
-    <t>fujitrax</t>
-  </si>
-  <si>
-    <t>KNOWLEDGE</t>
   </si>
 </sst>
 </file>
@@ -1233,1811 +1233,1817 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>144</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>145</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>147</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>148</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>149</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>150</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>151</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>152</v>
+        <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>154</v>
+        <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>155</v>
+        <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>156</v>
+        <v>13</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>281</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>157</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>158</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>158</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>158</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>150</v>
+        <v>7</v>
       </c>
       <c r="I2" t="s">
-        <v>159</v>
+        <v>18</v>
       </c>
       <c r="J2" t="s">
-        <v>158</v>
+        <v>16</v>
       </c>
       <c r="K2" t="s">
-        <v>159</v>
+        <v>18</v>
       </c>
       <c r="L2" t="s">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M2" t="s">
-        <v>155</v>
+        <v>12</v>
       </c>
       <c r="N2" t="s">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>281</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>161</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>162</v>
+        <v>24</v>
       </c>
       <c r="H3" t="s">
-        <v>163</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
-        <v>164</v>
+        <v>26</v>
       </c>
       <c r="J3" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="K3" t="s">
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="L3" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="M3" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="N3" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>165</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>166</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>165</v>
+        <v>28</v>
       </c>
       <c r="F4" t="s">
-        <v>167</v>
+        <v>30</v>
       </c>
       <c r="G4" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="H4" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="I4" t="s">
-        <v>151</v>
+        <v>8</v>
       </c>
       <c r="J4" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="K4" t="s">
-        <v>168</v>
+        <v>31</v>
       </c>
       <c r="L4" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="M4" t="s">
-        <v>169</v>
+        <v>33</v>
       </c>
       <c r="N4" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>170</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>144</v>
+        <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>161</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>147</v>
+        <v>4</v>
       </c>
       <c r="F5" t="s">
-        <v>171</v>
+        <v>36</v>
       </c>
       <c r="G5" t="s">
-        <v>167</v>
+        <v>30</v>
       </c>
       <c r="H5" t="s">
-        <v>172</v>
+        <v>37</v>
       </c>
       <c r="I5" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="J5" t="s">
-        <v>165</v>
+        <v>28</v>
       </c>
       <c r="K5" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="L5" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="M5" t="s">
-        <v>173</v>
+        <v>40</v>
       </c>
       <c r="N5" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>174</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>175</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="F6" t="s">
-        <v>176</v>
+        <v>45</v>
       </c>
       <c r="G6" t="s">
-        <v>171</v>
+        <v>36</v>
       </c>
       <c r="H6" t="s">
-        <v>177</v>
+        <v>46</v>
       </c>
       <c r="I6" t="s">
-        <v>178</v>
+        <v>47</v>
       </c>
       <c r="J6" t="s">
-        <v>144</v>
+        <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="L6" t="s">
-        <v>179</v>
+        <v>49</v>
       </c>
       <c r="M6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="N6" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>180</v>
+        <v>50</v>
       </c>
       <c r="B7" t="s">
-        <v>175</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E7" t="s">
-        <v>175</v>
+        <v>44</v>
       </c>
       <c r="F7" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="G7" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="H7" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="I7" t="s">
-        <v>163</v>
+        <v>25</v>
       </c>
       <c r="J7" t="s">
-        <v>147</v>
+        <v>4</v>
       </c>
       <c r="K7" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="L7" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="M7" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="N7" t="s">
-        <v>5</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>181</v>
+        <v>58</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>182</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
         <v>61</v>
       </c>
       <c r="E8" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="F8" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="G8" t="s">
-        <v>183</v>
+        <v>62</v>
       </c>
       <c r="H8" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="I8" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="J8" t="s">
-        <v>184</v>
+        <v>64</v>
       </c>
       <c r="K8" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="L8" t="s">
-        <v>185</v>
+        <v>66</v>
       </c>
       <c r="M8" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="N8" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>186</v>
+        <v>68</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G9" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" t="s">
         <v>73</v>
       </c>
-      <c r="D9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="J9" t="s">
+        <v>2</v>
+      </c>
+      <c r="K9" t="s">
+        <v>74</v>
+      </c>
+      <c r="L9" t="s">
         <v>75</v>
       </c>
-      <c r="G9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H9" t="s">
-        <v>36</v>
-      </c>
-      <c r="I9" t="s">
-        <v>8</v>
-      </c>
-      <c r="J9" t="s">
-        <v>145</v>
-      </c>
-      <c r="K9" t="s">
-        <v>115</v>
-      </c>
-      <c r="L9" t="s">
-        <v>187</v>
-      </c>
       <c r="M9" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="N9" t="s">
-        <v>7</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>188</v>
+        <v>77</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G10" t="s">
+        <v>71</v>
+      </c>
+      <c r="H10" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" t="s">
         <v>80</v>
       </c>
-      <c r="D10" t="s">
-        <v>182</v>
-      </c>
-      <c r="E10" t="s">
-        <v>56</v>
-      </c>
-      <c r="F10" t="s">
-        <v>189</v>
-      </c>
-      <c r="G10" t="s">
-        <v>75</v>
-      </c>
-      <c r="H10" t="s">
-        <v>170</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>9</v>
       </c>
-      <c r="J10" t="s">
-        <v>152</v>
-      </c>
       <c r="K10" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="L10" t="s">
-        <v>190</v>
+        <v>82</v>
       </c>
       <c r="M10" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="N10" t="s">
-        <v>8</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>191</v>
+        <v>83</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="E11" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F11" t="s">
-        <v>192</v>
+        <v>85</v>
       </c>
       <c r="G11" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="H11" t="s">
-        <v>193</v>
+        <v>87</v>
       </c>
       <c r="I11" t="s">
-        <v>157</v>
+        <v>15</v>
       </c>
       <c r="J11" t="s">
-        <v>161</v>
+        <v>22</v>
       </c>
       <c r="K11" t="s">
-        <v>194</v>
+        <v>88</v>
       </c>
       <c r="L11" t="s">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="M11" t="s">
-        <v>195</v>
+        <v>89</v>
       </c>
       <c r="N11" t="s">
-        <v>9</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>196</v>
+        <v>90</v>
       </c>
       <c r="B12" t="s">
         <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="E12" t="s">
         <v>61</v>
       </c>
       <c r="F12" t="s">
+        <v>86</v>
+      </c>
+      <c r="G12" t="s">
+        <v>93</v>
+      </c>
+      <c r="H12" t="s">
+        <v>94</v>
+      </c>
+      <c r="I12" t="s">
+        <v>95</v>
+      </c>
+      <c r="J12" t="s">
+        <v>96</v>
+      </c>
+      <c r="K12" t="s">
+        <v>97</v>
+      </c>
+      <c r="L12" t="s">
+        <v>15</v>
+      </c>
+      <c r="M12" t="s">
         <v>98</v>
       </c>
-      <c r="G12" t="s">
-        <v>128</v>
-      </c>
-      <c r="H12" t="s">
-        <v>57</v>
-      </c>
-      <c r="I12" t="s">
-        <v>10</v>
-      </c>
-      <c r="J12" t="s">
-        <v>197</v>
-      </c>
-      <c r="K12" t="s">
-        <v>142</v>
-      </c>
-      <c r="L12" t="s">
-        <v>157</v>
-      </c>
-      <c r="M12" t="s">
-        <v>198</v>
-      </c>
       <c r="N12" t="s">
-        <v>10</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" t="s">
+        <v>100</v>
+      </c>
+      <c r="D13" t="s">
         <v>70</v>
       </c>
-      <c r="C13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D13" t="s">
-        <v>73</v>
-      </c>
       <c r="E13" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="F13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G13" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="H13" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="I13" t="s">
-        <v>11</v>
+        <v>103</v>
       </c>
       <c r="J13" t="s">
-        <v>166</v>
+        <v>29</v>
       </c>
       <c r="K13" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="L13" t="s">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="M13" t="s">
-        <v>201</v>
+        <v>105</v>
       </c>
       <c r="N13" t="s">
-        <v>11</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>202</v>
+        <v>106</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D14" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="E14" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="F14" t="s">
-        <v>203</v>
+        <v>108</v>
       </c>
       <c r="G14" t="s">
-        <v>204</v>
+        <v>109</v>
       </c>
       <c r="H14" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="I14" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="J14" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K14" t="s">
-        <v>205</v>
+        <v>111</v>
       </c>
       <c r="L14" t="s">
-        <v>12</v>
+        <v>112</v>
       </c>
       <c r="M14" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="N14" t="s">
-        <v>12</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>206</v>
+        <v>113</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="D15" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="E15" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="F15" t="s">
-        <v>207</v>
+        <v>115</v>
       </c>
       <c r="G15" t="s">
-        <v>208</v>
+        <v>116</v>
       </c>
       <c r="H15" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="I15" t="s">
-        <v>209</v>
+        <v>117</v>
       </c>
       <c r="J15" t="s">
-        <v>30</v>
+        <v>118</v>
       </c>
       <c r="K15" t="s">
-        <v>210</v>
+        <v>119</v>
       </c>
       <c r="L15" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="M15" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="N15" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>211</v>
+        <v>120</v>
       </c>
       <c r="B16" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E16" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="F16" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="G16" t="s">
-        <v>212</v>
+        <v>121</v>
       </c>
       <c r="H16" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="I16" t="s">
-        <v>213</v>
+        <v>122</v>
       </c>
       <c r="J16" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="L16" t="s">
-        <v>14</v>
+        <v>123</v>
       </c>
       <c r="M16" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="N16" t="s">
-        <v>14</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>214</v>
+        <v>124</v>
       </c>
       <c r="B17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" t="s">
+        <v>93</v>
+      </c>
+      <c r="F17" t="s">
+        <v>102</v>
+      </c>
+      <c r="G17" t="s">
+        <v>125</v>
+      </c>
+      <c r="H17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I17" t="s">
+        <v>123</v>
+      </c>
+      <c r="J17" t="s">
+        <v>72</v>
+      </c>
+      <c r="L17" t="s">
+        <v>127</v>
+      </c>
+      <c r="M17" t="s">
+        <v>30</v>
+      </c>
+      <c r="N17" t="s">
         <v>128</v>
-      </c>
-      <c r="C17" t="s">
-        <v>102</v>
-      </c>
-      <c r="D17" t="s">
-        <v>87</v>
-      </c>
-      <c r="E17" t="s">
-        <v>128</v>
-      </c>
-      <c r="F17" t="s">
-        <v>129</v>
-      </c>
-      <c r="G17" t="s">
-        <v>215</v>
-      </c>
-      <c r="H17" t="s">
-        <v>82</v>
-      </c>
-      <c r="I17" t="s">
-        <v>14</v>
-      </c>
-      <c r="J17" t="s">
-        <v>36</v>
-      </c>
-      <c r="L17" t="s">
-        <v>16</v>
-      </c>
-      <c r="M17" t="s">
-        <v>167</v>
-      </c>
-      <c r="N17" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>216</v>
+        <v>129</v>
       </c>
       <c r="B18" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="D18" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E18" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="F18" t="s">
-        <v>204</v>
+        <v>109</v>
       </c>
       <c r="G18" t="s">
-        <v>217</v>
+        <v>131</v>
       </c>
       <c r="H18" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="I18" t="s">
-        <v>172</v>
+        <v>37</v>
       </c>
       <c r="J18" t="s">
-        <v>175</v>
+        <v>44</v>
       </c>
       <c r="L18" t="s">
-        <v>17</v>
+        <v>133</v>
       </c>
       <c r="M18" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="N18" t="s">
-        <v>16</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>218</v>
+        <v>134</v>
       </c>
       <c r="B19" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="D19" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="E19" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="F19" t="s">
-        <v>208</v>
+        <v>116</v>
       </c>
       <c r="G19" t="s">
-        <v>219</v>
+        <v>136</v>
       </c>
       <c r="H19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I19" t="s">
-        <v>16</v>
+        <v>127</v>
       </c>
       <c r="J19" t="s">
-        <v>220</v>
+        <v>137</v>
       </c>
       <c r="L19" t="s">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="M19" t="s">
         <v>61</v>
       </c>
       <c r="N19" t="s">
-        <v>17</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>204</v>
+        <v>109</v>
       </c>
       <c r="B20" t="s">
+        <v>139</v>
+      </c>
+      <c r="C20" t="s">
+        <v>74</v>
+      </c>
+      <c r="D20" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" t="s">
+        <v>139</v>
+      </c>
+      <c r="F20" t="s">
+        <v>121</v>
+      </c>
+      <c r="G20" t="s">
+        <v>140</v>
+      </c>
+      <c r="H20" t="s">
+        <v>65</v>
+      </c>
+      <c r="I20" t="s">
+        <v>40</v>
+      </c>
+      <c r="J20" t="s">
+        <v>59</v>
+      </c>
+      <c r="L20" t="s">
+        <v>17</v>
+      </c>
+      <c r="M20" t="s">
+        <v>53</v>
+      </c>
+      <c r="N20" t="s">
         <v>141</v>
-      </c>
-      <c r="C20" t="s">
-        <v>115</v>
-      </c>
-      <c r="D20" t="s">
-        <v>95</v>
-      </c>
-      <c r="E20" t="s">
-        <v>141</v>
-      </c>
-      <c r="F20" t="s">
-        <v>212</v>
-      </c>
-      <c r="G20" t="s">
-        <v>221</v>
-      </c>
-      <c r="H20" t="s">
-        <v>102</v>
-      </c>
-      <c r="I20" t="s">
-        <v>173</v>
-      </c>
-      <c r="J20" t="s">
-        <v>46</v>
-      </c>
-      <c r="L20" t="s">
-        <v>20</v>
-      </c>
-      <c r="M20" t="s">
-        <v>62</v>
-      </c>
-      <c r="N20" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>222</v>
+        <v>142</v>
       </c>
       <c r="B21" t="s">
-        <v>142</v>
+        <v>97</v>
+      </c>
+      <c r="C21" t="s">
+        <v>143</v>
       </c>
       <c r="D21" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="E21" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="F21" t="s">
-        <v>215</v>
+        <v>125</v>
       </c>
       <c r="G21" t="s">
-        <v>223</v>
+        <v>144</v>
       </c>
       <c r="H21" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="I21" t="s">
-        <v>17</v>
+        <v>133</v>
       </c>
       <c r="J21" t="s">
-        <v>170</v>
+        <v>34</v>
       </c>
       <c r="L21" t="s">
-        <v>21</v>
+        <v>146</v>
       </c>
       <c r="M21" t="s">
-        <v>183</v>
+        <v>62</v>
       </c>
       <c r="N21" t="s">
-        <v>19</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>224</v>
+        <v>147</v>
       </c>
       <c r="B22" t="s">
-        <v>274</v>
+        <v>148</v>
       </c>
       <c r="D22" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="E22" t="s">
-        <v>274</v>
+        <v>148</v>
       </c>
       <c r="F22" t="s">
-        <v>217</v>
+        <v>131</v>
       </c>
       <c r="G22" t="s">
-        <v>225</v>
+        <v>149</v>
       </c>
       <c r="H22" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
       <c r="I22" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J22" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="L22" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="M22" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="N22" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>226</v>
+        <v>151</v>
       </c>
       <c r="B23" t="s">
-        <v>279</v>
+        <v>152</v>
       </c>
       <c r="D23" t="s">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="E23" t="s">
-        <v>279</v>
+        <v>152</v>
       </c>
       <c r="F23" t="s">
-        <v>221</v>
+        <v>140</v>
       </c>
       <c r="G23" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="H23" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="I23" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="J23" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="L23" t="s">
-        <v>23</v>
+        <v>153</v>
       </c>
       <c r="M23" t="s">
-        <v>227</v>
+        <v>154</v>
       </c>
       <c r="N23" t="s">
-        <v>21</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>228</v>
+        <v>155</v>
       </c>
       <c r="D24" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="F24" t="s">
-        <v>229</v>
+        <v>156</v>
       </c>
       <c r="G24" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="H24" t="s">
-        <v>121</v>
+        <v>158</v>
       </c>
       <c r="I24" t="s">
-        <v>25</v>
+        <v>159</v>
       </c>
       <c r="J24" t="s">
-        <v>231</v>
+        <v>160</v>
       </c>
       <c r="L24" t="s">
-        <v>25</v>
+        <v>159</v>
       </c>
       <c r="M24" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="N24" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>232</v>
+        <v>161</v>
       </c>
       <c r="D25" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="F25" t="s">
-        <v>223</v>
+        <v>144</v>
       </c>
       <c r="G25" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="H25" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="I25" t="s">
-        <v>26</v>
+        <v>163</v>
       </c>
       <c r="J25" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="L25" t="s">
-        <v>26</v>
+        <v>163</v>
       </c>
       <c r="M25" t="s">
-        <v>67</v>
+        <v>164</v>
       </c>
       <c r="N25" t="s">
-        <v>23</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>212</v>
+        <v>121</v>
       </c>
       <c r="D26" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="F26" t="s">
-        <v>225</v>
+        <v>149</v>
       </c>
       <c r="G26" t="s">
-        <v>233</v>
+        <v>165</v>
       </c>
       <c r="H26" t="s">
-        <v>234</v>
+        <v>166</v>
       </c>
       <c r="I26" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="J26" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="L26" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="M26" t="s">
-        <v>235</v>
+        <v>168</v>
       </c>
       <c r="N26" t="s">
-        <v>24</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>236</v>
+        <v>170</v>
       </c>
       <c r="D27" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="F27" t="s">
-        <v>237</v>
+        <v>171</v>
       </c>
       <c r="G27" t="s">
-        <v>238</v>
+        <v>172</v>
       </c>
       <c r="H27" t="s">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="I27" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="J27" t="s">
         <v>61</v>
       </c>
       <c r="L27" t="s">
-        <v>28</v>
+        <v>174</v>
       </c>
       <c r="M27" t="s">
-        <v>182</v>
+        <v>60</v>
       </c>
       <c r="N27" t="s">
-        <v>25</v>
+        <v>159</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>239</v>
+        <v>175</v>
       </c>
       <c r="D28" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F28" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="G28" t="s">
-        <v>280</v>
+        <v>6</v>
       </c>
       <c r="H28" t="s">
-        <v>240</v>
+        <v>176</v>
       </c>
       <c r="I28" t="s">
-        <v>241</v>
+        <v>177</v>
       </c>
       <c r="J28" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="L28" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="M28" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="N28" t="s">
-        <v>26</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>242</v>
+        <v>178</v>
       </c>
       <c r="D29" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="F29" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="G29" t="s">
-        <v>162</v>
+        <v>24</v>
       </c>
       <c r="H29" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="I29" t="s">
-        <v>177</v>
+        <v>46</v>
       </c>
       <c r="J29" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="L29" t="s">
-        <v>243</v>
+        <v>180</v>
       </c>
       <c r="M29" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N29" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>244</v>
+        <v>181</v>
       </c>
       <c r="D30" t="s">
-        <v>245</v>
+        <v>182</v>
       </c>
       <c r="F30" t="s">
-        <v>233</v>
+        <v>165</v>
       </c>
       <c r="H30" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="I30" t="s">
-        <v>35</v>
+        <v>183</v>
       </c>
       <c r="J30" t="s">
-        <v>182</v>
+        <v>60</v>
       </c>
       <c r="L30" t="s">
-        <v>31</v>
+        <v>184</v>
       </c>
       <c r="M30" t="s">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="N30" t="s">
-        <v>28</v>
+        <v>174</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>246</v>
+        <v>185</v>
       </c>
       <c r="D31" t="s">
-        <v>273</v>
+        <v>186</v>
       </c>
       <c r="F31" t="s">
-        <v>247</v>
+        <v>187</v>
       </c>
       <c r="H31" t="s">
-        <v>216</v>
+        <v>129</v>
       </c>
       <c r="I31" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="J31" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="L31" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="M31" t="s">
-        <v>192</v>
+        <v>85</v>
       </c>
       <c r="N31" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>215</v>
+        <v>125</v>
       </c>
       <c r="D32" t="s">
-        <v>275</v>
+        <v>188</v>
       </c>
       <c r="F32" t="s">
-        <v>238</v>
+        <v>172</v>
       </c>
       <c r="H32" t="s">
-        <v>232</v>
+        <v>161</v>
       </c>
       <c r="I32" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="J32" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="L32" t="s">
-        <v>33</v>
+        <v>189</v>
       </c>
       <c r="M32" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N32" t="s">
-        <v>30</v>
+        <v>118</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>248</v>
+        <v>190</v>
       </c>
       <c r="D33" t="s">
-        <v>279</v>
+        <v>152</v>
       </c>
       <c r="H33" t="s">
-        <v>212</v>
+        <v>121</v>
       </c>
       <c r="I33" t="s">
-        <v>47</v>
+        <v>191</v>
       </c>
       <c r="J33" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="L33" t="s">
-        <v>249</v>
+        <v>192</v>
       </c>
       <c r="M33" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="N33" t="s">
-        <v>31</v>
+        <v>184</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>250</v>
+        <v>193</v>
+      </c>
+      <c r="D34" t="s">
+        <v>143</v>
       </c>
       <c r="H34" t="s">
-        <v>194</v>
+        <v>88</v>
       </c>
       <c r="I34" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="J34" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="L34" t="s">
-        <v>35</v>
+        <v>183</v>
       </c>
       <c r="M34" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="N34" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>251</v>
+        <v>194</v>
       </c>
       <c r="H35" t="s">
-        <v>251</v>
+        <v>194</v>
       </c>
       <c r="I35" t="s">
-        <v>53</v>
+        <v>195</v>
       </c>
       <c r="J35" t="s">
-        <v>79</v>
+        <v>196</v>
       </c>
       <c r="L35" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="M35" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="N35" t="s">
-        <v>33</v>
+        <v>189</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>252</v>
+        <v>197</v>
       </c>
       <c r="H36" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I36" t="s">
-        <v>54</v>
+        <v>198</v>
       </c>
       <c r="J36" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="L36" t="s">
-        <v>37</v>
+        <v>199</v>
       </c>
       <c r="M36" t="s">
-        <v>253</v>
+        <v>200</v>
       </c>
       <c r="N36" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>217</v>
+        <v>131</v>
       </c>
       <c r="H37" t="s">
-        <v>229</v>
+        <v>156</v>
       </c>
       <c r="I37" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="J37" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L37" t="s">
-        <v>254</v>
+        <v>201</v>
       </c>
       <c r="M37" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="N37" t="s">
-        <v>35</v>
+        <v>183</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>255</v>
+        <v>202</v>
       </c>
       <c r="H38" t="s">
-        <v>223</v>
+        <v>144</v>
       </c>
       <c r="I38" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="J38" t="s">
-        <v>84</v>
+        <v>203</v>
       </c>
       <c r="L38" t="s">
-        <v>39</v>
+        <v>204</v>
       </c>
       <c r="M38" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="N38" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>256</v>
+        <v>205</v>
       </c>
       <c r="H39" t="s">
-        <v>225</v>
+        <v>149</v>
       </c>
       <c r="I39" t="s">
-        <v>193</v>
+        <v>87</v>
       </c>
       <c r="J39" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="L39" t="s">
-        <v>40</v>
+        <v>206</v>
       </c>
       <c r="M39" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N39" t="s">
-        <v>37</v>
+        <v>199</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>257</v>
+        <v>207</v>
       </c>
       <c r="H40" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="I40" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="J40" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="L40" t="s">
-        <v>41</v>
+        <v>208</v>
       </c>
       <c r="M40" t="s">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="N40" t="s">
-        <v>38</v>
+        <v>209</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>219</v>
+        <v>136</v>
       </c>
       <c r="H41" t="s">
-        <v>233</v>
+        <v>165</v>
       </c>
       <c r="I41" t="s">
         <v>61</v>
       </c>
       <c r="J41" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="L41" t="s">
-        <v>45</v>
+        <v>210</v>
       </c>
       <c r="M41" t="s">
-        <v>258</v>
+        <v>211</v>
       </c>
       <c r="N41" t="s">
-        <v>39</v>
+        <v>204</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>259</v>
+        <v>212</v>
       </c>
       <c r="H42" t="s">
-        <v>238</v>
+        <v>172</v>
       </c>
       <c r="I42" t="s">
-        <v>63</v>
+        <v>213</v>
       </c>
       <c r="J42" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="L42" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="M42" t="s">
-        <v>203</v>
+        <v>108</v>
       </c>
       <c r="N42" t="s">
-        <v>40</v>
+        <v>206</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>221</v>
+        <v>140</v>
       </c>
       <c r="I43" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="J43" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="L43" t="s">
-        <v>260</v>
+        <v>214</v>
       </c>
       <c r="M43" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="N43" t="s">
-        <v>41</v>
+        <v>208</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>261</v>
+        <v>215</v>
       </c>
       <c r="I44" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="J44" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L44" t="s">
-        <v>47</v>
+        <v>191</v>
       </c>
       <c r="M44" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="N44" t="s">
-        <v>42</v>
+        <v>216</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>262</v>
+        <v>217</v>
       </c>
       <c r="I45" t="s">
-        <v>67</v>
+        <v>164</v>
       </c>
       <c r="J45" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="L45" t="s">
-        <v>48</v>
+        <v>218</v>
       </c>
       <c r="M45" t="s">
-        <v>276</v>
+        <v>219</v>
       </c>
       <c r="N45" t="s">
-        <v>43</v>
+        <v>220</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>263</v>
+        <v>221</v>
       </c>
       <c r="I46" t="s">
-        <v>68</v>
+        <v>222</v>
       </c>
       <c r="J46" t="s">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="L46" t="s">
-        <v>49</v>
+        <v>223</v>
       </c>
       <c r="N46" t="s">
-        <v>44</v>
+        <v>224</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I47" t="s">
-        <v>182</v>
+        <v>60</v>
       </c>
       <c r="J47" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="L47" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="N47" t="s">
-        <v>45</v>
+        <v>210</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I48" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="J48" t="s">
-        <v>108</v>
+        <v>225</v>
       </c>
       <c r="L48" t="s">
-        <v>54</v>
+        <v>198</v>
       </c>
       <c r="N48" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
     </row>
     <row r="49" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I49" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="J49" t="s">
+        <v>83</v>
+      </c>
+      <c r="L49" t="s">
+        <v>69</v>
+      </c>
+      <c r="N49" t="s">
         <v>191</v>
-      </c>
-      <c r="L49" t="s">
-        <v>55</v>
-      </c>
-      <c r="N49" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="50" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I50" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J50" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="L50" t="s">
-        <v>264</v>
+        <v>226</v>
       </c>
       <c r="N50" t="s">
-        <v>48</v>
+        <v>218</v>
       </c>
     </row>
     <row r="51" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I51" t="s">
+        <v>48</v>
+      </c>
+      <c r="J51" t="s">
+        <v>227</v>
+      </c>
+      <c r="L51" t="s">
         <v>78</v>
       </c>
-      <c r="J51" t="s">
-        <v>116</v>
-      </c>
-      <c r="L51" t="s">
-        <v>56</v>
-      </c>
       <c r="N51" t="s">
-        <v>49</v>
+        <v>223</v>
       </c>
     </row>
     <row r="52" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I52" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="J52" t="s">
-        <v>117</v>
+        <v>228</v>
       </c>
       <c r="L52" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="N52" t="s">
-        <v>50</v>
+        <v>229</v>
       </c>
     </row>
     <row r="53" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I53" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J53" t="s">
-        <v>118</v>
+        <v>230</v>
       </c>
       <c r="L53" t="s">
-        <v>59</v>
+        <v>231</v>
       </c>
       <c r="N53" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
     </row>
     <row r="54" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I54" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="J54" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="L54" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="N54" t="s">
-        <v>52</v>
+        <v>232</v>
       </c>
     </row>
     <row r="55" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I55" t="s">
+        <v>107</v>
+      </c>
+      <c r="J55" t="s">
         <v>93</v>
-      </c>
-      <c r="J55" t="s">
-        <v>128</v>
       </c>
       <c r="L55" t="s">
         <v>61</v>
       </c>
       <c r="N55" t="s">
-        <v>53</v>
+        <v>195</v>
       </c>
     </row>
     <row r="56" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I56" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="J56" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="L56" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="N56" t="s">
-        <v>54</v>
+        <v>198</v>
       </c>
     </row>
     <row r="57" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I57" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="J57" t="s">
-        <v>240</v>
+        <v>176</v>
       </c>
       <c r="L57" t="s">
-        <v>63</v>
+        <v>213</v>
       </c>
       <c r="N57" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
     </row>
     <row r="58" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I58" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="J58" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="L58" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="N58" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
     </row>
     <row r="59" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I59" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J59" t="s">
-        <v>265</v>
+        <v>233</v>
       </c>
       <c r="L59" t="s">
-        <v>65</v>
+        <v>234</v>
       </c>
       <c r="N59" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
     </row>
     <row r="60" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I60" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="J60" t="s">
-        <v>212</v>
+        <v>121</v>
       </c>
       <c r="L60" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="N60" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="61" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I61" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="J61" t="s">
-        <v>261</v>
+        <v>215</v>
       </c>
       <c r="L61" t="s">
-        <v>67</v>
+        <v>164</v>
       </c>
       <c r="N61" t="s">
-        <v>59</v>
+        <v>231</v>
       </c>
     </row>
     <row r="62" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I62" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="J62" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L62" t="s">
-        <v>68</v>
+        <v>222</v>
       </c>
       <c r="N62" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="63" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I63" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J63" t="s">
-        <v>225</v>
+        <v>149</v>
       </c>
       <c r="L63" t="s">
-        <v>69</v>
+        <v>235</v>
       </c>
       <c r="N63" t="s">
         <v>61</v>
@@ -3045,610 +3051,610 @@
     </row>
     <row r="64" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I64" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="J64" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="L64" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="N64" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="65" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I65" t="s">
-        <v>266</v>
+        <v>236</v>
       </c>
       <c r="J65" t="s">
-        <v>267</v>
+        <v>237</v>
       </c>
       <c r="L65" t="s">
-        <v>71</v>
+        <v>238</v>
       </c>
       <c r="N65" t="s">
-        <v>63</v>
+        <v>213</v>
       </c>
     </row>
     <row r="66" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I66" t="s">
-        <v>277</v>
+        <v>239</v>
       </c>
       <c r="J66" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="L66" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="N66" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
     </row>
     <row r="67" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I67" t="s">
-        <v>278</v>
+        <v>240</v>
       </c>
       <c r="J67" t="s">
-        <v>279</v>
+        <v>152</v>
       </c>
       <c r="L67" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N67" t="s">
-        <v>65</v>
+        <v>234</v>
       </c>
     </row>
     <row r="68" spans="9:14" x14ac:dyDescent="0.3">
       <c r="L68" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="N68" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
     </row>
     <row r="69" spans="9:14" x14ac:dyDescent="0.3">
       <c r="L69" t="s">
-        <v>76</v>
+        <v>241</v>
       </c>
       <c r="N69" t="s">
-        <v>67</v>
+        <v>164</v>
       </c>
     </row>
     <row r="70" spans="9:14" x14ac:dyDescent="0.3">
       <c r="L70" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="N70" t="s">
-        <v>68</v>
+        <v>222</v>
       </c>
     </row>
     <row r="71" spans="9:14" x14ac:dyDescent="0.3">
       <c r="L71" t="s">
-        <v>79</v>
+        <v>196</v>
       </c>
       <c r="N71" t="s">
-        <v>69</v>
+        <v>235</v>
       </c>
     </row>
     <row r="72" spans="9:14" x14ac:dyDescent="0.3">
       <c r="L72" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="N72" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
     </row>
     <row r="73" spans="9:14" x14ac:dyDescent="0.3">
       <c r="L73" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N73" t="s">
-        <v>71</v>
+        <v>238</v>
       </c>
     </row>
     <row r="74" spans="9:14" x14ac:dyDescent="0.3">
       <c r="L74" t="s">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="N74" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
     </row>
     <row r="75" spans="9:14" x14ac:dyDescent="0.3">
       <c r="L75" t="s">
-        <v>85</v>
+        <v>242</v>
       </c>
       <c r="N75" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="76" spans="9:14" x14ac:dyDescent="0.3">
       <c r="L76" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="N76" t="s">
-        <v>74</v>
+        <v>243</v>
       </c>
     </row>
     <row r="77" spans="9:14" x14ac:dyDescent="0.3">
       <c r="L77" t="s">
-        <v>88</v>
+        <v>244</v>
       </c>
       <c r="N77" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="78" spans="9:14" x14ac:dyDescent="0.3">
       <c r="L78" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="N78" t="s">
-        <v>76</v>
+        <v>241</v>
       </c>
     </row>
     <row r="79" spans="9:14" x14ac:dyDescent="0.3">
       <c r="L79" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="N79" t="s">
-        <v>77</v>
+        <v>246</v>
       </c>
     </row>
     <row r="80" spans="9:14" x14ac:dyDescent="0.3">
       <c r="L80" t="s">
-        <v>92</v>
+        <v>247</v>
       </c>
       <c r="N80" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
     </row>
     <row r="81" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L81" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="N81" t="s">
-        <v>79</v>
+        <v>196</v>
       </c>
     </row>
     <row r="82" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L82" t="s">
-        <v>94</v>
+        <v>248</v>
       </c>
       <c r="N82" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
     </row>
     <row r="83" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L83" t="s">
-        <v>253</v>
+        <v>200</v>
       </c>
       <c r="N83" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="84" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L84" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="N84" t="s">
-        <v>82</v>
+        <v>126</v>
       </c>
     </row>
     <row r="85" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L85" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="N85" t="s">
-        <v>83</v>
+        <v>249</v>
       </c>
     </row>
     <row r="86" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L86" t="s">
-        <v>97</v>
+        <v>250</v>
       </c>
       <c r="N86" t="s">
-        <v>84</v>
+        <v>203</v>
       </c>
     </row>
     <row r="87" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L87" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="N87" t="s">
-        <v>85</v>
+        <v>242</v>
       </c>
     </row>
     <row r="88" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L88" t="s">
-        <v>99</v>
+        <v>251</v>
       </c>
       <c r="N88" t="s">
-        <v>86</v>
+        <v>252</v>
       </c>
     </row>
     <row r="89" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L89" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N89" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="90" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L90" t="s">
-        <v>101</v>
+        <v>253</v>
       </c>
       <c r="N90" t="s">
-        <v>88</v>
+        <v>244</v>
       </c>
     </row>
     <row r="91" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L91" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="N91" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
     </row>
     <row r="92" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L92" t="s">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="N92" t="s">
-        <v>90</v>
+        <v>254</v>
       </c>
     </row>
     <row r="93" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L93" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="N93" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
     </row>
     <row r="94" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L94" t="s">
-        <v>107</v>
+        <v>255</v>
       </c>
       <c r="N94" t="s">
-        <v>92</v>
+        <v>247</v>
       </c>
     </row>
     <row r="95" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L95" t="s">
-        <v>108</v>
+        <v>225</v>
       </c>
       <c r="N95" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="96" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L96" t="s">
-        <v>109</v>
+        <v>256</v>
       </c>
       <c r="N96" t="s">
-        <v>94</v>
+        <v>248</v>
       </c>
     </row>
     <row r="97" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L97" t="s">
-        <v>110</v>
+        <v>257</v>
       </c>
       <c r="N97" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
     </row>
     <row r="98" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L98" t="s">
-        <v>111</v>
+        <v>258</v>
       </c>
       <c r="N98" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
     </row>
     <row r="99" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L99" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="N99" t="s">
-        <v>97</v>
+        <v>250</v>
       </c>
     </row>
     <row r="100" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L100" t="s">
-        <v>113</v>
+        <v>259</v>
       </c>
       <c r="N100" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
     </row>
     <row r="101" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L101" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
       <c r="N101" t="s">
-        <v>99</v>
+        <v>251</v>
       </c>
     </row>
     <row r="102" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L102" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="N102" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="103" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L103" t="s">
-        <v>116</v>
+        <v>227</v>
       </c>
       <c r="N103" t="s">
-        <v>101</v>
+        <v>253</v>
       </c>
     </row>
     <row r="104" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L104" t="s">
-        <v>117</v>
+        <v>228</v>
       </c>
       <c r="N104" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
     </row>
     <row r="105" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L105" t="s">
-        <v>118</v>
+        <v>230</v>
       </c>
       <c r="N105" t="s">
-        <v>103</v>
+        <v>260</v>
       </c>
     </row>
     <row r="106" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L106" t="s">
-        <v>119</v>
+        <v>261</v>
       </c>
       <c r="N106" t="s">
-        <v>104</v>
+        <v>130</v>
       </c>
     </row>
     <row r="107" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L107" t="s">
-        <v>120</v>
+        <v>262</v>
       </c>
       <c r="N107" t="s">
-        <v>105</v>
+        <v>263</v>
       </c>
     </row>
     <row r="108" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L108" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="N108" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
     </row>
     <row r="109" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L109" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="N109" t="s">
-        <v>107</v>
+        <v>255</v>
       </c>
     </row>
     <row r="110" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L110" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="N110" t="s">
-        <v>108</v>
+        <v>225</v>
       </c>
     </row>
     <row r="111" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L111" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="N111" t="s">
-        <v>109</v>
+        <v>256</v>
       </c>
     </row>
     <row r="112" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L112" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="N112" t="s">
-        <v>110</v>
+        <v>257</v>
       </c>
     </row>
     <row r="113" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L113" t="s">
-        <v>234</v>
+        <v>166</v>
       </c>
       <c r="N113" t="s">
-        <v>111</v>
+        <v>258</v>
       </c>
     </row>
     <row r="114" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L114" t="s">
-        <v>126</v>
+        <v>268</v>
       </c>
       <c r="N114" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
     </row>
     <row r="115" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L115" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="N115" t="s">
-        <v>113</v>
+        <v>259</v>
       </c>
     </row>
     <row r="116" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L116" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="N116" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
     </row>
     <row r="117" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L117" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="N117" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
     </row>
     <row r="118" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L118" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="N118" t="s">
-        <v>116</v>
+        <v>227</v>
       </c>
     </row>
     <row r="119" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L119" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="N119" t="s">
-        <v>117</v>
+        <v>228</v>
       </c>
     </row>
     <row r="120" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L120" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="N120" t="s">
-        <v>118</v>
+        <v>230</v>
       </c>
     </row>
     <row r="121" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L121" t="s">
-        <v>277</v>
+        <v>239</v>
       </c>
       <c r="N121" t="s">
-        <v>119</v>
+        <v>261</v>
       </c>
     </row>
     <row r="122" spans="12:14" x14ac:dyDescent="0.3">
       <c r="N122" t="s">
-        <v>120</v>
+        <v>262</v>
       </c>
     </row>
     <row r="123" spans="12:14" x14ac:dyDescent="0.3">
       <c r="N123" t="s">
-        <v>121</v>
+        <v>158</v>
       </c>
     </row>
     <row r="124" spans="12:14" x14ac:dyDescent="0.3">
       <c r="N124" t="s">
-        <v>122</v>
+        <v>270</v>
       </c>
     </row>
     <row r="125" spans="12:14" x14ac:dyDescent="0.3">
       <c r="N125" t="s">
-        <v>123</v>
+        <v>271</v>
       </c>
     </row>
     <row r="126" spans="12:14" x14ac:dyDescent="0.3">
       <c r="N126" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
     </row>
     <row r="127" spans="12:14" x14ac:dyDescent="0.3">
       <c r="N127" t="s">
-        <v>125</v>
+        <v>272</v>
       </c>
     </row>
     <row r="128" spans="12:14" x14ac:dyDescent="0.3">
       <c r="N128" t="s">
-        <v>126</v>
+        <v>268</v>
       </c>
     </row>
     <row r="129" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N129" t="s">
-        <v>127</v>
+        <v>273</v>
       </c>
     </row>
     <row r="130" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N130" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
     </row>
     <row r="131" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N131" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
     </row>
     <row r="132" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N132" t="s">
-        <v>130</v>
+        <v>274</v>
       </c>
     </row>
     <row r="133" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N133" t="s">
-        <v>131</v>
+        <v>275</v>
       </c>
     </row>
     <row r="134" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N134" t="s">
-        <v>132</v>
+        <v>173</v>
       </c>
     </row>
     <row r="135" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N135" t="s">
-        <v>133</v>
+        <v>276</v>
       </c>
     </row>
     <row r="136" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N136" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
     </row>
     <row r="137" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N137" t="s">
-        <v>135</v>
+        <v>277</v>
       </c>
     </row>
     <row r="138" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N138" t="s">
-        <v>136</v>
+        <v>278</v>
       </c>
     </row>
     <row r="139" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N139" t="s">
-        <v>137</v>
+        <v>279</v>
       </c>
     </row>
     <row r="140" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N140" t="s">
-        <v>138</v>
+        <v>280</v>
       </c>
     </row>
     <row r="141" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N141" t="s">
-        <v>139</v>
+        <v>281</v>
       </c>
     </row>
     <row r="142" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N142" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
     </row>
     <row r="143" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N143" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="144" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N144" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
     </row>
     <row r="145" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N145" t="s">
-        <v>277</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
